--- a/sheets/대금율보/검수/아리랑 행진곡.xlsx
+++ b/sheets/대금율보/검수/아리랑 행진곡.xlsx
@@ -4763,8 +4763,7 @@
       <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-ㄴ
-‹</t>
+ㄴ</t>
         </is>
       </c>
       <c r="O6" s="26"/>
@@ -4960,8 +4959,7 @@
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="E10" s="26" t="inlineStr">
@@ -4971,8 +4969,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G10" s="26" t="inlineStr">
@@ -5255,8 +5252,7 @@
       <c r="O14" s="26"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="Q14" s="26"/>

--- a/sheets/대금율보/검수/아리랑 행진곡.xlsx
+++ b/sheets/대금율보/검수/아리랑 행진곡.xlsx
@@ -4452,28 +4452,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="72.04" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="72.04" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="72.04" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="Q5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="72.04" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="Q6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="72.04" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="Q7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="72.04" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -4889,7 +4889,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="72.04" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -4948,7 +4948,7 @@
       <c r="P9" s="21"/>
       <c r="Q9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="72.04" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Q10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="72.04" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="Q11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="72.04" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -5129,7 +5129,7 @@
       <c r="P12" s="21"/>
       <c r="Q12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="72.04" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="72.04" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="26"/>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="Q14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="72.04" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="Q15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="72.04" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="Q16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="72.04" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="Q17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="72.04" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="26"/>
@@ -5512,6 +5512,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>